--- a/ProyectoTasasMercantil/plantilla_bloomberg/historico/BloombergHistorico_TasasMercantil_FULL.xlsx
+++ b/ProyectoTasasMercantil/plantilla_bloomberg/historico/BloombergHistorico_TasasMercantil_FULL.xlsx
@@ -898,35 +898,35 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("ED1 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED1 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("ED2 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED2 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("ED3 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED3 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("ED4 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED4 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>BDH("ED5 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED5 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="K4" s="10">
-        <f>BDH("ED6 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED6 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="M4" s="10">
-        <f>BDH("ED7 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED7 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="O4" s="10">
-        <f>BDH("ED8 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("ED8 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -1142,35 +1142,35 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("SFR1 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR1 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("SFR2 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR2 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("SFR3 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR3 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("SFR4 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR4 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>BDH("SFR5 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR5 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="K4" s="10">
-        <f>BDH("SFR6 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR6 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="M4" s="10">
-        <f>BDH("SFR7 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR7 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="O4" s="10">
-        <f>BDH("SFR8 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SFR8 Comdty","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -1852,47 +1852,47 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("USGG1M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG1M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("USGG3M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG3M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("USGG6M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG6M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USGG12M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG12M Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>BDH("USGG2YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG2YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="K4" s="10">
-        <f>BDH("USGG3YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG3YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="M4" s="10">
-        <f>BDH("USGG5YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG5YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="O4" s="10">
-        <f>BDH("USGG7YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG7YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="Q4" s="10">
-        <f>BDH("USGG10YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG10YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="S4" s="10">
-        <f>BDH("USGG20YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG20YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="U4" s="10">
-        <f>BDH("USGG30YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGG30YR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2090,19 +2090,19 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("USGGT05Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGT05Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("USGGT10Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGT10Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("USGGT20Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGT20Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USGGT30Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGT30Y Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2230,19 +2230,19 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("USGGBE02 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGBE02 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("USGGBE05 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGBE05 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("USGGBE10 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGBE10 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USGGBE30 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USGGBE30 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2370,19 +2370,19 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("USOSFR2 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR2 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("USOSFR5 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR5 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("USOSFR10 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR10 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USOSFR30 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR30 BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2510,19 +2510,19 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("USSW2 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USSW2 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("USSW5 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USSW5 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("USSW10 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USSW10 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USSW30 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USSW30 Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2686,31 +2686,31 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("SOFRRATE Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SOFRRATE Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("SOFR30A Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SOFR30A Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("SOFR90A Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("SOFR90A Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("USOSFR1Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR1Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>BDH("USOSFR3Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR3Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="K4" s="10">
-        <f>BDH("USOSFR6Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR6Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="M4" s="10">
-        <f>BDH("USOSFR12Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("USOSFR12Z BGN Curncy","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
@@ -2892,27 +2892,27 @@
     </row>
     <row r="4">
       <c r="A4" s="10">
-        <f>BDH("FDTR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("FDTR Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>BDH("FDFD Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("FDFD Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>BDH("FEDFUND Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("FEDFUND Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>BDH("FEDL01 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("FEDL01 Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>BDH("FRRRIORB Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("FRRRIORB Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
       <c r="K4" s="10">
-        <f>BDH("RRPONTSY Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=H","Fill=B","cols=2;rows=12000")</f>
+        <f>BDH("RRPONTSY Index","PX_LAST",'01_Parametros'!$B$3,'01_Parametros'!$B$4,"Dir=V","Dts=S","Fill=B","cols=2;rows=12000")</f>
         <v/>
       </c>
     </row>
